--- a/regist.php 単体テスト仕様書.xlsx
+++ b/regist.php 単体テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="133">
   <si>
     <t>テスト区分</t>
   </si>
@@ -187,6 +187,9 @@
 アカウント権限        一般</t>
   </si>
   <si>
+    <t>「名前（名）が未入力です。」赤字表示</t>
+  </si>
+  <si>
     <t>カナ（姓）未入力</t>
   </si>
   <si>
@@ -235,43 +238,424 @@
     <t>「カナ（名）が未入力です。」赤字表示</t>
   </si>
   <si>
-    <t>メール未入力</t>
-  </si>
-  <si>
-    <t>メール空欄で送信</t>
+    <t>メールアドレス未入力</t>
+  </si>
+  <si>
+    <t>メールアドレス空欄で送信</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        空欄
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
   </si>
   <si>
     <t>エラー表示</t>
   </si>
   <si>
+    <t>パスワード未入力</t>
+  </si>
+  <si>
+    <t>パスワード空欄で送信</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        空欄
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>郵便番号未入力</t>
+  </si>
+  <si>
+    <t>郵便番号空欄で送信</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        空欄
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
     <t>全項目未入力</t>
   </si>
   <si>
     <t>全て空欄で送信</t>
   </si>
   <si>
-    <t>全項目にエラー表示</t>
+    <t>項目        空欄
+名前（姓）        空欄
+名前（名）        空欄
+カナ（姓）        空欄
+カナ（名）        空欄
+メールアドレス        空欄
+パスワード       空欄
+性別        空欄
+郵便番号        空欄
+都道府県        空欄
+市区町村        空欄
+番地        空欄
+アカウント権限        空欄</t>
+  </si>
+  <si>
+    <t>全項目に赤字でエラー表示</t>
   </si>
   <si>
     <t>入力形式チェック</t>
   </si>
   <si>
-    <t>姓形式</t>
+    <t>名前（姓）形式</t>
   </si>
   <si>
     <t>半角英字入力</t>
   </si>
   <si>
-    <t>「ひらがな・漢字のみ入力可」表示</t>
-  </si>
-  <si>
-    <t>カナ形式</t>
+    <t>項目        入力値
+名前（姓）        tanaka
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>「名前（姓）はひらがな・漢字のみ入力できます。」表示</t>
+  </si>
+  <si>
+    <t>全角英字入力</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        ｔａｎａｋａ
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>半角数字入力</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        123
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>半角英字・ひらがな入力</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        taなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>名前（名）形式</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        tarou
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>「名前（名）はひらがな・漢字のみ入力できます。」表示</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）      ｔａｒｏｕ
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        123
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        taろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>カナ（性）形式</t>
   </si>
   <si>
     <t>ひらがな入力</t>
   </si>
   <si>
-    <t>「カタカナのみ入力可」表示</t>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        たなか
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>「カナ（姓）はカタカナのみ入力できます。」と表示</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        tanaka
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）       ｔａｎａｋａ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        123
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        taなか
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>漢字入力</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        田中
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>カナ（名）形式</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        tarou
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>「カナ（名）はカタカナのみ入力できます。」表示</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       ｔａｒｏｕ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       123
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       taろう
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       太郎
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
   </si>
   <si>
     <t>パスワード形式</t>
@@ -280,7 +664,70 @@
     <t>全角入力</t>
   </si>
   <si>
-    <t>「半角英数字のみ入力可」表示</t>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       タロウ
+メールアドレス        test@gmail.com
+パスワード        ＳＳＳＳＳＳ
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>「パスワードは半角英数字のみ入力できます。」表示</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       タロウ
+メールアドレス        test@gmail.com
+パスワード        暗号
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       タロウ
+メールアドレス        test@gmail.com
+パスワード        あんごう
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>カタカナ入力</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       タロウ
+メールアドレス        test@gmail.com
+パスワード        アンゴウ
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
   </si>
   <si>
     <t>郵便番号形式</t>
@@ -289,36 +736,213 @@
     <t>英字入力</t>
   </si>
   <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        abcdefg
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        ゆうびんばんごう
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        ユウビンバンゴウ
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>住所（市区町村）形式</t>
+  </si>
+  <si>
+    <t>記号（ハイフンとスペース）以外の記号</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        !"#$%&amp;'(
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>「住所（市区町村）に使用できない文字があります。」と表示</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村       ａｓａｈｉｋａｗａｓｈｉ
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>住所（番地）形式</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地         !"#$%&amp;'(
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>「住所（番地）に使用できない文字があります。」と表示</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        ａｉｕｅｏ１－２－３
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        aiueo1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>姓11文字</t>
+  </si>
+  <si>
+    <t>11文字入力</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなかたなかたなかたなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）       タロウ
+メールアドレス        test@gmail.com
+パスワード        ＳＳＳＳＳＳ
+性別        男
+郵便番号        ユウビンバンゴウ
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>入力不可 or エラー表示</t>
+  </si>
+  <si>
+    <t>名11文字</t>
+  </si>
+  <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろうたろうたろうたろう
+カナ（姓）        タナカ
+カナ（名）       タロウ
+メールアドレス        test@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        ユウビンバンゴウ
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>メール1文字</t>
+  </si>
+  <si>
+    <t>1文字入力</t>
+  </si>
+  <si>
     <t>文字数チェック</t>
   </si>
   <si>
-    <t>姓11文字</t>
-  </si>
-  <si>
-    <t>11文字入力</t>
-  </si>
-  <si>
-    <t>入力不可 or エラー表示</t>
-  </si>
-  <si>
     <t>メール101文字</t>
   </si>
   <si>
     <t>101文字入力</t>
   </si>
   <si>
+    <t>メールアドレスの形式が正しくありませんと表示</t>
+  </si>
+  <si>
+    <t>正常遷移</t>
+  </si>
+  <si>
+    <t>正常入力後送信</t>
+  </si>
+  <si>
+    <t>regist_confirm.phpへ遷移</t>
+  </si>
+  <si>
     <t>画面遷移</t>
   </si>
   <si>
-    <t>正常遷移</t>
-  </si>
-  <si>
-    <t>正常入力後送信</t>
-  </si>
-  <si>
-    <t>regist_confirm.phpへ遷移</t>
-  </si>
-  <si>
     <t>エラー時遷移</t>
   </si>
   <si>
@@ -326,9 +950,6 @@
   </si>
   <si>
     <t>同画面に留まりエラー表示</t>
-  </si>
-  <si>
-    <t>入力する画面をすべて記入する</t>
   </si>
 </sst>
 </file>
@@ -694,7 +1315,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="16.63"/>
+    <col customWidth="1" min="3" max="3" width="18.88"/>
     <col customWidth="1" min="4" max="4" width="28.0"/>
     <col customWidth="1" min="5" max="6" width="32.13"/>
     <col customWidth="1" min="7" max="7" width="9.13"/>
@@ -874,7 +1495,7 @@
         <v>33</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="15"/>
@@ -888,16 +1509,16 @@
         <v>6.0</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="12"/>
       <c r="H8" s="15"/>
@@ -911,16 +1532,16 @@
         <v>7.0</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="15"/>
@@ -934,14 +1555,16 @@
         <v>8.0</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="12"/>
+        <v>44</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="F10" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G10" s="12"/>
       <c r="H10" s="15"/>
@@ -950,19 +1573,21 @@
       <c r="K10" s="8"/>
     </row>
     <row r="11">
-      <c r="A11" s="16"/>
+      <c r="A11" s="14"/>
       <c r="B11" s="5">
         <v>9.0</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D11" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12" t="s">
-        <v>47</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="15"/>
@@ -971,63 +1596,69 @@
       <c r="K11" s="8"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="s">
-        <v>48</v>
-      </c>
+      <c r="A12" s="14"/>
       <c r="B12" s="5">
         <v>10.0</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5" t="s">
+      <c r="D12" s="12" t="s">
         <v>51</v>
       </c>
+      <c r="E12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>46</v>
+      </c>
       <c r="G12" s="12"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="5"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="12"/>
       <c r="K12" s="8"/>
     </row>
     <row r="13">
-      <c r="A13" s="14"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="5">
         <v>11.0</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5" t="s">
+      <c r="D13" s="12" t="s">
         <v>54</v>
       </c>
+      <c r="E13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>56</v>
+      </c>
       <c r="G13" s="12"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="5"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="12"/>
       <c r="K13" s="8"/>
     </row>
     <row r="14">
-      <c r="A14" s="14"/>
+      <c r="A14" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="B14" s="5">
         <v>12.0</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="5"/>
+        <v>59</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="F14" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G14" s="12"/>
       <c r="H14" s="7"/>
@@ -1036,7 +1667,7 @@
       <c r="K14" s="8"/>
     </row>
     <row r="15">
-      <c r="A15" s="16"/>
+      <c r="A15" s="14"/>
       <c r="B15" s="5">
         <v>13.0</v>
       </c>
@@ -1044,11 +1675,13 @@
         <v>58</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="5"/>
+        <v>62</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="F15" s="5" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G15" s="12"/>
       <c r="H15" s="7"/>
@@ -1057,42 +1690,44 @@
       <c r="K15" s="8"/>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="s">
-        <v>60</v>
-      </c>
+      <c r="A16" s="14"/>
       <c r="B16" s="12">
         <v>14.0</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="G16" s="12"/>
       <c r="H16" s="7"/>
-      <c r="I16" s="5"/>
+      <c r="I16" s="8"/>
       <c r="J16" s="5"/>
       <c r="K16" s="8"/>
     </row>
     <row r="17">
-      <c r="A17" s="16"/>
+      <c r="A17" s="14"/>
       <c r="B17" s="12">
         <v>15.0</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="F17" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G17" s="12"/>
       <c r="H17" s="7"/>
@@ -1101,57 +1736,810 @@
       <c r="K17" s="8"/>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="s">
-        <v>66</v>
-      </c>
+      <c r="A18" s="14"/>
       <c r="B18" s="12">
         <v>16.0</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="12" t="s">
+      <c r="C18" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12" t="s">
+      <c r="D18" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>69</v>
       </c>
+      <c r="F18" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="G18" s="12"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="5"/>
       <c r="K18" s="8"/>
     </row>
     <row r="19">
-      <c r="A19" s="18"/>
+      <c r="A19" s="14"/>
       <c r="B19" s="12">
         <v>17.0</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12" t="s">
+      <c r="G19" s="12"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14"/>
+      <c r="B20" s="12">
+        <v>18.0</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="8"/>
-    </row>
-    <row r="20">
-      <c r="D20" s="13" t="s">
+      <c r="F20" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="12"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="8"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14"/>
+      <c r="B21" s="12">
+        <v>19.0</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>73</v>
       </c>
+      <c r="F21" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="8"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14"/>
+      <c r="B22" s="12">
+        <v>20.0</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="12"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="8"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14"/>
+      <c r="B23" s="12">
+        <v>21.0</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="8"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14"/>
+      <c r="B24" s="12">
+        <v>22.0</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="12"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="8"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14"/>
+      <c r="B25" s="12">
+        <v>23.0</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="8"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14"/>
+      <c r="B26" s="12">
+        <v>24.0</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="12"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14"/>
+      <c r="B27" s="12">
+        <v>25.0</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="12"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="8"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14"/>
+      <c r="B28" s="12">
+        <v>26.0</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G28" s="12"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="8"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14"/>
+      <c r="B29" s="12">
+        <v>27.0</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29" s="12"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="8"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14"/>
+      <c r="B30" s="12">
+        <v>28.0</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" s="12"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="8"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14"/>
+      <c r="B31" s="12">
+        <v>29.0</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G31" s="12"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="8"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14"/>
+      <c r="B32" s="12">
+        <v>30.0</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G32" s="12"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="8"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14"/>
+      <c r="B33" s="12">
+        <v>31.0</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="12"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="8"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14"/>
+      <c r="B34" s="12">
+        <v>32.0</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="12"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="8"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14"/>
+      <c r="B35" s="12">
+        <v>33.0</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" s="12"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="8"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14"/>
+      <c r="B36" s="12">
+        <v>34.0</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="12"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="8"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14"/>
+      <c r="B37" s="12">
+        <v>35.0</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G37" s="12"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="8"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14"/>
+      <c r="B38" s="12">
+        <v>36.0</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G38" s="12"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="8"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14"/>
+      <c r="B39" s="12">
+        <v>37.0</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G39" s="12"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="8"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14"/>
+      <c r="B40" s="12">
+        <v>38.0</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G40" s="12"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="8"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14"/>
+      <c r="B41" s="12">
+        <v>39.0</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G41" s="12"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="8"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="14"/>
+      <c r="B42" s="12">
+        <v>40.0</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G42" s="12"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="8"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="14"/>
+      <c r="B43" s="12">
+        <v>41.0</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G43" s="12"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="8"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14"/>
+      <c r="B44" s="12">
+        <v>42.0</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G44" s="12"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="8"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="14"/>
+      <c r="B45" s="12">
+        <v>43.0</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G45" s="12"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="8"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="14"/>
+      <c r="B46" s="12">
+        <v>44.0</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G46" s="12"/>
+      <c r="H46" s="7"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="8"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="14"/>
+      <c r="B47" s="12">
+        <v>45.0</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="G47" s="12"/>
+      <c r="H47" s="7"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="8"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16"/>
+      <c r="B48" s="12">
+        <v>46.0</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="8"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B49" s="12">
+        <v>47.0</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G49" s="12"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="8"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16"/>
+      <c r="B50" s="12">
+        <v>48.0</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G50" s="12"/>
+      <c r="H50" s="7"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="8"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" s="12">
+        <v>49.0</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G51" s="12"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="8"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="18"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="8"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="G2:G17 H18:H19">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="G2:G50 H51:H52">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/regist.php 単体テスト仕様書.xlsx
+++ b/regist.php 単体テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="135">
   <si>
     <t>テスト区分</t>
   </si>
@@ -919,6 +919,24 @@
     <t>1文字入力</t>
   </si>
   <si>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス        t
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
+  </si>
+  <si>
+    <t>メールアドレスの形式が正しくありませんと表示</t>
+  </si>
+  <si>
     <t>文字数チェック</t>
   </si>
   <si>
@@ -928,7 +946,19 @@
     <t>101文字入力</t>
   </si>
   <si>
-    <t>メールアドレスの形式が正しくありませんと表示</t>
+    <t>項目        入力値
+名前（姓）        たなか
+名前（名）        たろう
+カナ（姓）        タナカ
+カナ（名）        タロウ
+メールアドレス      x9qL7mV2zR8tYp4Kj3sN6wFx0dH5uBc1eT8gLp9rQ2vZm7aSd4fGh6Jk1nRt8yUv3pWx0cZ5bNm2qLs7tR4vY8k@example.com@gmail.com
+パスワード        ssssss
+性別        男
+郵便番号        1234567
+都道府県        北海道
+市区町村        旭川市
+番地        あいうえお1-2-3
+アカウント権限        一般</t>
   </si>
   <si>
     <t>正常遷移</t>
@@ -1042,7 +1072,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1091,12 +1121,6 @@
     </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2436,8 +2460,12 @@
       <c r="D48" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+      <c r="E48" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>123</v>
+      </c>
       <c r="G48" s="12"/>
       <c r="H48" s="7"/>
       <c r="I48" s="8"/>
@@ -2446,20 +2474,22 @@
     </row>
     <row r="49">
       <c r="A49" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B49" s="12">
         <v>47.0</v>
       </c>
       <c r="C49" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="G49" s="12"/>
       <c r="H49" s="7"/>
@@ -2473,14 +2503,16 @@
         <v>48.0</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="E50" s="12"/>
+        <v>129</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="F50" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G50" s="12"/>
       <c r="H50" s="7"/>
@@ -2489,21 +2521,23 @@
       <c r="K50" s="8"/>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="s">
-        <v>129</v>
+      <c r="A51" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="B51" s="12">
         <v>49.0</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E51" s="12"/>
+        <v>133</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="F51" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G51" s="12"/>
       <c r="H51" s="15"/>
@@ -2511,35 +2545,9 @@
       <c r="J51" s="12"/>
       <c r="K51" s="8"/>
     </row>
-    <row r="52">
-      <c r="A52" s="18"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="8"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="G2:G50 H51:H52">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="G2:G50 H51">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/regist.php 単体テスト仕様書.xlsx
+++ b/regist.php 単体テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="96">
   <si>
     <t>テスト区分</t>
   </si>
@@ -74,6 +74,13 @@
     <t>姓未入力</t>
   </si>
   <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（姓）は何も入力せず、名前（姓）以外の欄は値を入力する。
+⑤画面下部にある「確認する」を押下。</t>
+  </si>
+  <si>
     <t>「名前（姓）が未入力です。」赤字表示</t>
   </si>
   <si>
@@ -83,13 +90,24 @@
     <t>名前未入力</t>
   </si>
   <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（名）は何も入力せず、名前（名）以外の欄は値を入力する。
+⑤画面下部にある「確認する」を押下。</t>
+  </si>
+  <si>
     <t>「名前（名）が未入力です。」赤字表示</t>
   </si>
   <si>
     <t>カナ（姓）未入力</t>
   </si>
   <si>
-    <t>カナ（姓）のみ空欄で送信</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（姓）は何も入力せず、カナ（姓）以外の欄は値を入力する。
+⑤画面下部にある「確認する」を押下。</t>
   </si>
   <si>
     <t>「カナ（姓）が未入力です。」赤字表示</t>
@@ -98,7 +116,11 @@
     <t>カナ（名）未入力</t>
   </si>
   <si>
-    <t>カナ（名）のみ空欄で送信</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（名）は何も入力せず、カナ（名）以外の欄は値を入力する。
+⑤画面下部にある「確認する」を押下。</t>
   </si>
   <si>
     <t>「カナ（名）が未入力です。」赤字表示</t>
@@ -107,94 +129,145 @@
     <t>メールアドレス未入力</t>
   </si>
   <si>
-    <t>メールアドレス空欄で送信</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④メールアドレスは何も入力せず、メールアドレス以外の欄は値を入力する。
+⑤画面下部にある「確認する」を押下。</t>
+  </si>
+  <si>
+    <t>「メールアドレスが未入力です。」赤字表示</t>
+  </si>
+  <si>
+    <t>パスワード未入力</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④パスワードは何も入力せず、パスワード以外の欄は値を入力する。
+⑤画面下部にある「確認する」を押下。</t>
+  </si>
+  <si>
+    <t>「パスワードが未入力です。」赤字表示</t>
+  </si>
+  <si>
+    <t>郵便番号未入力</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④郵便番号は何も入力せず、郵便番号以外の欄は値を入力する。
+⑤画面下部にある「確認する」を押下。</t>
+  </si>
+  <si>
+    <t>「郵便番号が未入力です。」赤字表示</t>
+  </si>
+  <si>
+    <t>住所（市区町村）未入力</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④住所（市区町村）は何も入力せず、住所（市区町村）以外の欄は値を入力する。
+⑤画面下部にある「確認する」を押下。</t>
+  </si>
+  <si>
+    <t>「住所（市区町村）が未入力です。」赤字表示</t>
+  </si>
+  <si>
+    <t>住所（番地）未入力</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④住所（番地）は何も入力せず、住所（番地）以外の欄は値を入力する。
+⑤画面下部にある「確認する」を押下。</t>
+  </si>
+  <si>
+    <t>「住所（番地）が未入力です。」赤字表示</t>
+  </si>
+  <si>
+    <t>全項目未入力</t>
+  </si>
+  <si>
+    <t>全項目に赤字でエラー表示</t>
+  </si>
+  <si>
+    <t>名前（姓）形式</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（姓）を入力時に半角英字入力で値を入力する。
+⑤名前（姓）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>「名前（姓）はひらがな・漢字のみ入力できます。」表示</t>
+  </si>
+  <si>
+    <t>入力形式チェック</t>
+  </si>
+  <si>
+    <t>全角英字入力</t>
+  </si>
+  <si>
+    <t>半角数字入力</t>
+  </si>
+  <si>
+    <t>半角英字・ひらがな入力</t>
+  </si>
+  <si>
+    <t>名前（名）形式</t>
+  </si>
+  <si>
+    <t>半角英字入力</t>
+  </si>
+  <si>
+    <t>「名前（名）はひらがな・漢字のみ入力できます。」表示</t>
+  </si>
+  <si>
+    <t>カナ（性）形式</t>
+  </si>
+  <si>
+    <t>ひらがな入力</t>
+  </si>
+  <si>
+    <t>「カナ（姓）はカタカナのみ入力できます。」と表示</t>
+  </si>
+  <si>
+    <t>漢字入力</t>
+  </si>
+  <si>
+    <t>カナ（名）形式</t>
+  </si>
+  <si>
+    <t>「カナ（名）はカタカナのみ入力できます。」表示</t>
+  </si>
+  <si>
+    <t>パスワード形式</t>
+  </si>
+  <si>
+    <t>全角入力</t>
+  </si>
+  <si>
+    <t>「パスワードは半角英数字のみ入力できます。」表示</t>
+  </si>
+  <si>
+    <t>カタカナ入力</t>
+  </si>
+  <si>
+    <t>郵便番号形式</t>
+  </si>
+  <si>
+    <t>英字入力</t>
   </si>
   <si>
     <t>エラー表示</t>
-  </si>
-  <si>
-    <t>パスワード未入力</t>
-  </si>
-  <si>
-    <t>パスワード空欄で送信</t>
-  </si>
-  <si>
-    <t>郵便番号未入力</t>
-  </si>
-  <si>
-    <t>郵便番号空欄で送信</t>
-  </si>
-  <si>
-    <t>全項目未入力</t>
-  </si>
-  <si>
-    <t>全て空欄で送信</t>
-  </si>
-  <si>
-    <t>全項目に赤字でエラー表示</t>
-  </si>
-  <si>
-    <t>名前（姓）形式</t>
-  </si>
-  <si>
-    <t>半角英字入力</t>
-  </si>
-  <si>
-    <t>「名前（姓）はひらがな・漢字のみ入力できます。」表示</t>
-  </si>
-  <si>
-    <t>入力形式チェック</t>
-  </si>
-  <si>
-    <t>全角英字入力</t>
-  </si>
-  <si>
-    <t>半角数字入力</t>
-  </si>
-  <si>
-    <t>半角英字・ひらがな入力</t>
-  </si>
-  <si>
-    <t>名前（名）形式</t>
-  </si>
-  <si>
-    <t>「名前（名）はひらがな・漢字のみ入力できます。」表示</t>
-  </si>
-  <si>
-    <t>カナ（性）形式</t>
-  </si>
-  <si>
-    <t>ひらがな入力</t>
-  </si>
-  <si>
-    <t>「カナ（姓）はカタカナのみ入力できます。」と表示</t>
-  </si>
-  <si>
-    <t>漢字入力</t>
-  </si>
-  <si>
-    <t>カナ（名）形式</t>
-  </si>
-  <si>
-    <t>「カナ（名）はカタカナのみ入力できます。」表示</t>
-  </si>
-  <si>
-    <t>パスワード形式</t>
-  </si>
-  <si>
-    <t>全角入力</t>
-  </si>
-  <si>
-    <t>「パスワードは半角英数字のみ入力できます。」表示</t>
-  </si>
-  <si>
-    <t>カタカナ入力</t>
-  </si>
-  <si>
-    <t>郵便番号形式</t>
-  </si>
-  <si>
-    <t>英字入力</t>
   </si>
   <si>
     <t>住所（市区町村）形式</t>
@@ -631,7 +704,7 @@
   <cols>
     <col customWidth="1" min="3" max="3" width="18.88"/>
     <col customWidth="1" min="4" max="4" width="60.13"/>
-    <col customWidth="1" min="5" max="5" width="32.13"/>
+    <col customWidth="1" min="5" max="5" width="36.38"/>
     <col customWidth="1" min="6" max="6" width="9.13"/>
     <col customWidth="1" min="7" max="7" width="8.88"/>
     <col customWidth="1" min="8" max="8" width="8.13"/>
@@ -743,10 +816,10 @@
         <v>18</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="5"/>
@@ -756,19 +829,19 @@
     </row>
     <row r="6">
       <c r="A6" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="11">
         <v>5.0</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="8"/>
@@ -782,13 +855,13 @@
         <v>5.0</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="15"/>
@@ -802,13 +875,13 @@
         <v>6.0</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="15"/>
@@ -822,13 +895,13 @@
         <v>7.0</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="15"/>
@@ -842,13 +915,13 @@
         <v>8.0</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="15"/>
@@ -862,13 +935,13 @@
         <v>9.0</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F11" s="11"/>
       <c r="G11" s="15"/>
@@ -882,13 +955,13 @@
         <v>10.0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="15"/>
@@ -897,18 +970,18 @@
       <c r="J12" s="8"/>
     </row>
     <row r="13">
-      <c r="A13" s="16"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="5">
         <v>11.0</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>39</v>
+      <c r="C13" s="11" t="s">
+        <v>43</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>45</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="15"/>
@@ -917,60 +990,60 @@
       <c r="J13" s="8"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="s">
-        <v>42</v>
-      </c>
+      <c r="A14" s="14"/>
       <c r="B14" s="5">
         <v>12.0</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>39</v>
+      <c r="C14" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>41</v>
+        <v>12</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>47</v>
       </c>
       <c r="F14" s="11"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="5"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="11"/>
       <c r="J14" s="8"/>
     </row>
     <row r="15">
-      <c r="A15" s="14"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="5">
         <v>13.0</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F15" s="11"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="5"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="11"/>
       <c r="J15" s="8"/>
     </row>
     <row r="16">
-      <c r="A16" s="14"/>
+      <c r="A16" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="B16" s="11">
         <v>14.0</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F16" s="11"/>
       <c r="G16" s="7"/>
@@ -984,13 +1057,13 @@
         <v>15.0</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F17" s="11"/>
       <c r="G17" s="7"/>
@@ -1004,13 +1077,13 @@
         <v>16.0</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="7"/>
@@ -1024,13 +1097,13 @@
         <v>17.0</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="7"/>
@@ -1044,13 +1117,13 @@
         <v>18.0</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F20" s="11"/>
       <c r="G20" s="7"/>
@@ -1064,13 +1137,13 @@
         <v>19.0</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F21" s="11"/>
       <c r="G21" s="7"/>
@@ -1084,13 +1157,13 @@
         <v>20.0</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F22" s="11"/>
       <c r="G22" s="7"/>
@@ -1104,13 +1177,13 @@
         <v>21.0</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="7"/>
@@ -1124,13 +1197,13 @@
         <v>22.0</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="7"/>
@@ -1144,13 +1217,13 @@
         <v>23.0</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F25" s="11"/>
       <c r="G25" s="7"/>
@@ -1164,13 +1237,13 @@
         <v>24.0</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F26" s="11"/>
       <c r="G26" s="7"/>
@@ -1184,13 +1257,13 @@
         <v>25.0</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="7"/>
@@ -1204,13 +1277,13 @@
         <v>26.0</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="7"/>
@@ -1224,13 +1297,13 @@
         <v>27.0</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F29" s="11"/>
       <c r="G29" s="7"/>
@@ -1244,13 +1317,13 @@
         <v>28.0</v>
       </c>
       <c r="C30" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="E30" s="5" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F30" s="11"/>
       <c r="G30" s="7"/>
@@ -1264,13 +1337,13 @@
         <v>29.0</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F31" s="11"/>
       <c r="G31" s="7"/>
@@ -1284,13 +1357,13 @@
         <v>30.0</v>
       </c>
       <c r="C32" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>55</v>
-      </c>
       <c r="E32" s="5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F32" s="11"/>
       <c r="G32" s="7"/>
@@ -1304,13 +1377,13 @@
         <v>31.0</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F33" s="11"/>
       <c r="G33" s="7"/>
@@ -1324,13 +1397,13 @@
         <v>32.0</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="7"/>
@@ -1344,13 +1417,13 @@
         <v>33.0</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="7"/>
@@ -1364,13 +1437,13 @@
         <v>34.0</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="F36" s="11"/>
       <c r="G36" s="7"/>
@@ -1384,13 +1457,13 @@
         <v>35.0</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="F37" s="11"/>
       <c r="G37" s="7"/>
@@ -1404,13 +1477,13 @@
         <v>36.0</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="F38" s="11"/>
       <c r="G38" s="7"/>
@@ -1424,13 +1497,13 @@
         <v>37.0</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F39" s="11"/>
       <c r="G39" s="7"/>
@@ -1444,13 +1517,13 @@
         <v>38.0</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F40" s="11"/>
       <c r="G40" s="7"/>
@@ -1464,13 +1537,13 @@
         <v>39.0</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="F41" s="11"/>
       <c r="G41" s="7"/>
@@ -1484,13 +1557,13 @@
         <v>40.0</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F42" s="11"/>
       <c r="G42" s="7"/>
@@ -1504,13 +1577,13 @@
         <v>41.0</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F43" s="11"/>
       <c r="G43" s="7"/>
@@ -1524,13 +1597,13 @@
         <v>42.0</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="F44" s="11"/>
       <c r="G44" s="7"/>
@@ -1544,13 +1617,13 @@
         <v>43.0</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F45" s="11"/>
       <c r="G45" s="7"/>
@@ -1564,13 +1637,13 @@
         <v>44.0</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F46" s="11"/>
       <c r="G46" s="7"/>
@@ -1584,13 +1657,13 @@
         <v>45.0</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F47" s="11"/>
       <c r="G47" s="7"/>
@@ -1599,18 +1672,18 @@
       <c r="J47" s="8"/>
     </row>
     <row r="48">
-      <c r="A48" s="16"/>
+      <c r="A48" s="14"/>
       <c r="B48" s="11">
         <v>46.0</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F48" s="11"/>
       <c r="G48" s="7"/>
@@ -1619,24 +1692,22 @@
       <c r="J48" s="8"/>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="s">
-        <v>74</v>
-      </c>
+      <c r="A49" s="14"/>
       <c r="B49" s="11">
         <v>47.0</v>
       </c>
-      <c r="C49" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>77</v>
+      <c r="C49" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="F49" s="11"/>
       <c r="G49" s="7"/>
-      <c r="H49" s="5"/>
+      <c r="H49" s="8"/>
       <c r="I49" s="5"/>
       <c r="J49" s="8"/>
     </row>
@@ -1645,14 +1716,14 @@
       <c r="B50" s="11">
         <v>48.0</v>
       </c>
-      <c r="C50" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>80</v>
+      <c r="C50" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="F50" s="11"/>
       <c r="G50" s="7"/>
@@ -1661,30 +1732,72 @@
       <c r="J50" s="8"/>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="s">
-        <v>81</v>
+      <c r="A51" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="B51" s="11">
         <v>49.0</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>84</v>
+      <c r="C51" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="F51" s="11"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
       <c r="J51" s="8"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="16"/>
+      <c r="B52" s="11">
+        <v>50.0</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" s="11"/>
+      <c r="G52" s="7"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="8"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B53" s="11">
+        <v>51.0</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F53" s="11"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="8"/>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F50 G51">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F52 G53">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/regist.php 単体テスト仕様書.xlsx
+++ b/regist.php 単体テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="133">
   <si>
     <t>テスト区分</t>
   </si>
@@ -68,7 +68,7 @@
     <t>初期表示（都道府県）</t>
   </si>
   <si>
-    <t>空欄選択済</t>
+    <t>何も選択していない状態でも、空欄が選択済になっている。</t>
   </si>
   <si>
     <t>姓未入力</t>
@@ -197,7 +197,8 @@
     <t>全項目に赤字でエラー表示</t>
   </si>
   <si>
-    <t>名前（姓）形式</t>
+    <t>名前（姓）形式
+半角英字入力時のエラー</t>
   </si>
   <si>
     <t>①index.htmlをエクスプローラーで表示する。
@@ -213,94 +214,359 @@
     <t>入力形式チェック</t>
   </si>
   <si>
-    <t>全角英字入力</t>
-  </si>
-  <si>
-    <t>半角数字入力</t>
-  </si>
-  <si>
-    <t>半角英字・ひらがな入力</t>
-  </si>
-  <si>
-    <t>名前（名）形式</t>
-  </si>
-  <si>
-    <t>半角英字入力</t>
+    <t>名前（姓）形式
+全角英字入力時のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（姓）を入力時に全角英字入力で値を入力する。
+⑤名前（姓）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>名前（姓）形式
+半角数字入力時のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（姓）を入力時に半角数字入力で値を入力する。
+⑤名前（姓）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>名前（姓）形式
+半角英字とひらがな入力時のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（姓）を入力時に半角英字とひらがなを組み合わせた値を入力する。
+⑤名前（姓）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（姓）を入力時に半角英字の値を入力する。
+⑤名前（姓）以外の欄に値を入力する。</t>
   </si>
   <si>
     <t>「名前（名）はひらがな・漢字のみ入力できます。」表示</t>
   </si>
   <si>
-    <t>カナ（性）形式</t>
-  </si>
-  <si>
-    <t>ひらがな入力</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（姓）を入力時に全角英字入力の値を入力する。
+⑤名前（姓）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名前（姓）を入力時に半角数字入力の値を入力する。
+⑤名前（姓）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>名前（名）形式
+半角英字・ひらがな入力時のエラー</t>
+  </si>
+  <si>
+    <t>カナ（性）形式
+ひらがな入力時のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（性）を入力時にひらがなの値を入力する。
+⑤カナ（性）以外の欄に値を入力する。</t>
   </si>
   <si>
     <t>「カナ（姓）はカタカナのみ入力できます。」と表示</t>
   </si>
   <si>
-    <t>漢字入力</t>
-  </si>
-  <si>
-    <t>カナ（名）形式</t>
+    <t>カナ（性）形式
+半角英字入力時のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（性）を入力時に半角英字の値を入力する。
+⑤カナ（性）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>カナ（性）形式
+半角数字入力時のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（性）を入力時に半角数字の値を入力する。
+⑤カナ（性）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>カナ（性）形式
+半角英字・ひらがな入力時のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（性）を入力時に半角英字・ひらがなを組み合わせた値を入力する。
+⑤カナ（性）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>カナ（性）形式
+漢字入力時のエラー</t>
+  </si>
+  <si>
+    <t>カナ（名）形式
+半角英字入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（名）を入力時に半角英字の値を入力する。
+⑤カナ（名）以外の欄に値を入力する。</t>
   </si>
   <si>
     <t>「カナ（名）はカタカナのみ入力できます。」表示</t>
   </si>
   <si>
-    <t>パスワード形式</t>
-  </si>
-  <si>
-    <t>全角入力</t>
+    <t>カナ（名）形式
+全角英字入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（名）を入力時に全角英字の値を入力する。
+⑤カナ（名）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>カナ（名）形式
+半角数字入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（名）を入力時に半角数字の値を入力する。
+⑤カナ（名）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>カナ（名）形式
+半角英字・ひらがな入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（名）を入力時に半角英字・ひらがなを組み合わせた値を入力する。
+⑤カナ（名）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>カナ（名）形式
+漢字入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④カナ（名）を入力時に漢字の値を入力する。
+⑤カナ（名）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>パスワード形式
+全角入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④パスワードを入力時に全角入力の値を入力する。
+⑤パスワード以外の欄に値を入力する。</t>
   </si>
   <si>
     <t>「パスワードは半角英数字のみ入力できます。」表示</t>
   </si>
   <si>
-    <t>カタカナ入力</t>
-  </si>
-  <si>
-    <t>郵便番号形式</t>
-  </si>
-  <si>
-    <t>英字入力</t>
+    <t>パスワード形式
+漢字入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④パスワードを入力時に漢字入力の値を入力する。
+⑤パスワード以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>パスワード形式
+ひらがな入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④パスワードを入力時にひらがなの値を入力する。
+⑤パスワード以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>パスワード形式
+カタカナ入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④パスワードを入力時にカタカナの値を入力する。
+⑤パスワード以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>郵便番号形式
+英字入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④郵便番号を入力時に英字の値を入力する。
+⑤郵便番号以外の欄に値を入力する。</t>
   </si>
   <si>
     <t>エラー表示</t>
   </si>
   <si>
-    <t>住所（市区町村）形式</t>
-  </si>
-  <si>
-    <t>記号（ハイフンとスペース）以外の記号</t>
+    <t>郵便番号形式
+ひらがな入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④郵便番号を入力時にひらがなの値を入力する。
+⑤郵便番号以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>郵便番号形式
+カタカナ入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④郵便番号を入力時にカタカナの値を入力する。
+⑤郵便番号以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>住所（市区町村）形式
+記号（ハイフンとスペース）以外の記号入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④住所（市区町村）を入力時にカタカナの値を入力する。
+⑤住所（市区町村）以外の欄に値を入力する。</t>
   </si>
   <si>
     <t>「住所（市区町村）に使用できない文字があります。」と表示</t>
   </si>
   <si>
-    <t>住所（番地）形式</t>
+    <t>住所（市区町村）形式
+全角英字入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④住所（市区町村）を入力時に全角英字の値を入力する。
+⑤住所（市区町村）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>住所（市区町村）形式
+半角英字入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④住所（市区町村）を入力時に半角英字の値を入力する。
+⑤住所（市区町村）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>住所（番地）形式
+記号（ハイフンとスペース）以外の記号
+のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④住所（番地）を入力時に記号（ハイフンとスペース）以外の記号の値を入力する。
+⑤住所（番地）以外の欄に値を入力する。</t>
   </si>
   <si>
     <t>「住所（番地）に使用できない文字があります。」と表示</t>
   </si>
   <si>
-    <t>姓11文字</t>
-  </si>
-  <si>
-    <t>11文字入力</t>
+    <t>住所（番地）形式
+全角英字入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④住所（番地）を入力時に全角英字の値を入力する。
+⑤住所（番地）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>住所（番地）形式
+半角英字入力のエラー</t>
+  </si>
+  <si>
+    <t>姓11文字
+11文字以上の入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④姓を入力時に11文字以上の値を入力する。
+⑤姓以外の欄に値を入力する。</t>
   </si>
   <si>
     <t>入力不可 or エラー表示</t>
   </si>
   <si>
-    <t>名11文字</t>
-  </si>
-  <si>
-    <t>メール1文字</t>
-  </si>
-  <si>
-    <t>1文字入力</t>
+    <t>名11文字
+11文字以上の入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④名を入力時に11文字以上の値を入力する。
+⑤名以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>メールアドレス1文字
+1文字のみの入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④メールアドレスを入力時に1文字のみの値を入力する。
+⑤メールアドレス以外の欄に値を入力する。</t>
   </si>
   <si>
     <t>メールアドレスの形式が正しくありませんと表示</t>
@@ -309,9 +575,6 @@
     <t>メール101文字</t>
   </si>
   <si>
-    <t>101文字入力</t>
-  </si>
-  <si>
     <t>文字数チェック</t>
   </si>
   <si>
@@ -327,7 +590,7 @@
     <t>エラー時遷移</t>
   </si>
   <si>
-    <t>未入力送信</t>
+    <t>すべて未入力送信</t>
   </si>
   <si>
     <t>同画面に留まりエラー表示</t>
@@ -1037,15 +1300,15 @@
         <v>14.0</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="11"/>
+      <c r="F16" s="5"/>
       <c r="G16" s="7"/>
       <c r="H16" s="8"/>
       <c r="I16" s="5"/>
@@ -1057,15 +1320,15 @@
         <v>15.0</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="11"/>
+      <c r="F17" s="5"/>
       <c r="G17" s="7"/>
       <c r="H17" s="8"/>
       <c r="I17" s="5"/>
@@ -1077,15 +1340,15 @@
         <v>16.0</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F18" s="11"/>
+      <c r="F18" s="5"/>
       <c r="G18" s="7"/>
       <c r="H18" s="8"/>
       <c r="I18" s="5"/>
@@ -1097,15 +1360,15 @@
         <v>17.0</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="F19" s="5"/>
       <c r="G19" s="7"/>
       <c r="H19" s="8"/>
       <c r="I19" s="5"/>
@@ -1117,15 +1380,15 @@
         <v>18.0</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F20" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="F20" s="5"/>
       <c r="G20" s="7"/>
       <c r="H20" s="8"/>
       <c r="I20" s="5"/>
@@ -1137,15 +1400,15 @@
         <v>19.0</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="F21" s="5"/>
       <c r="G21" s="7"/>
       <c r="H21" s="8"/>
       <c r="I21" s="5"/>
@@ -1157,15 +1420,15 @@
         <v>20.0</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="F22" s="5"/>
       <c r="G22" s="7"/>
       <c r="H22" s="8"/>
       <c r="I22" s="5"/>
@@ -1177,15 +1440,15 @@
         <v>21.0</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F23" s="11"/>
+        <v>65</v>
+      </c>
+      <c r="F23" s="5"/>
       <c r="G23" s="7"/>
       <c r="H23" s="8"/>
       <c r="I23" s="5"/>
@@ -1197,15 +1460,15 @@
         <v>22.0</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F24" s="11"/>
+        <v>65</v>
+      </c>
+      <c r="F24" s="5"/>
       <c r="G24" s="7"/>
       <c r="H24" s="8"/>
       <c r="I24" s="5"/>
@@ -1217,15 +1480,15 @@
         <v>23.0</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="11"/>
+        <v>65</v>
+      </c>
+      <c r="F25" s="5"/>
       <c r="G25" s="7"/>
       <c r="H25" s="8"/>
       <c r="I25" s="5"/>
@@ -1237,15 +1500,15 @@
         <v>24.0</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F26" s="11"/>
+        <v>65</v>
+      </c>
+      <c r="F26" s="5"/>
       <c r="G26" s="7"/>
       <c r="H26" s="8"/>
       <c r="I26" s="5"/>
@@ -1257,13 +1520,13 @@
         <v>25.0</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F27" s="11"/>
       <c r="G27" s="7"/>
@@ -1277,13 +1540,13 @@
         <v>26.0</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F28" s="11"/>
       <c r="G28" s="7"/>
@@ -1297,13 +1560,13 @@
         <v>27.0</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F29" s="11"/>
       <c r="G29" s="7"/>
@@ -1317,13 +1580,13 @@
         <v>28.0</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F30" s="11"/>
       <c r="G30" s="7"/>
@@ -1337,13 +1600,13 @@
         <v>29.0</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F31" s="11"/>
       <c r="G31" s="7"/>
@@ -1357,13 +1620,13 @@
         <v>30.0</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F32" s="11"/>
       <c r="G32" s="7"/>
@@ -1377,13 +1640,13 @@
         <v>31.0</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F33" s="11"/>
       <c r="G33" s="7"/>
@@ -1397,13 +1660,13 @@
         <v>32.0</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F34" s="11"/>
       <c r="G34" s="7"/>
@@ -1417,13 +1680,13 @@
         <v>33.0</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F35" s="11"/>
       <c r="G35" s="7"/>
@@ -1437,13 +1700,13 @@
         <v>34.0</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F36" s="11"/>
       <c r="G36" s="7"/>
@@ -1457,13 +1720,13 @@
         <v>35.0</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="F37" s="11"/>
       <c r="G37" s="7"/>
@@ -1477,13 +1740,13 @@
         <v>36.0</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F38" s="11"/>
       <c r="G38" s="7"/>
@@ -1497,13 +1760,13 @@
         <v>37.0</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F39" s="11"/>
       <c r="G39" s="7"/>
@@ -1517,13 +1780,13 @@
         <v>38.0</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="F40" s="11"/>
       <c r="G40" s="7"/>
@@ -1537,13 +1800,13 @@
         <v>39.0</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="F41" s="11"/>
       <c r="G41" s="7"/>
@@ -1557,13 +1820,13 @@
         <v>40.0</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="F42" s="11"/>
       <c r="G42" s="7"/>
@@ -1577,13 +1840,13 @@
         <v>41.0</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>56</v>
+        <v>106</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="F43" s="11"/>
       <c r="G43" s="7"/>
@@ -1597,13 +1860,13 @@
         <v>42.0</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="F44" s="11"/>
       <c r="G44" s="7"/>
@@ -1617,13 +1880,13 @@
         <v>43.0</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="F45" s="11"/>
       <c r="G45" s="7"/>
@@ -1637,13 +1900,13 @@
         <v>44.0</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="F46" s="11"/>
       <c r="G46" s="7"/>
@@ -1657,13 +1920,13 @@
         <v>45.0</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="F47" s="11"/>
       <c r="G47" s="7"/>
@@ -1677,13 +1940,13 @@
         <v>46.0</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="F48" s="11"/>
       <c r="G48" s="7"/>
@@ -1697,13 +1960,13 @@
         <v>47.0</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="F49" s="11"/>
       <c r="G49" s="7"/>
@@ -1717,13 +1980,13 @@
         <v>48.0</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="F50" s="11"/>
       <c r="G50" s="7"/>
@@ -1733,19 +1996,19 @@
     </row>
     <row r="51">
       <c r="A51" s="13" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="B51" s="11">
         <v>49.0</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="F51" s="11"/>
       <c r="G51" s="7"/>
@@ -1759,13 +2022,13 @@
         <v>50.0</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="F52" s="11"/>
       <c r="G52" s="7"/>
@@ -1775,19 +2038,19 @@
     </row>
     <row r="53">
       <c r="A53" s="11" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="B53" s="11">
         <v>51.0</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="F53" s="11"/>
       <c r="G53" s="15"/>
@@ -1797,7 +2060,7 @@
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F52 G53">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F15 F27:F52 G53">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/regist.php 単体テスト仕様書.xlsx
+++ b/regist.php 単体テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="144">
   <si>
     <t>テスト区分</t>
   </si>
@@ -59,6 +59,15 @@
     <t>「男」が選択済みになっている。</t>
   </si>
   <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>早川</t>
+  </si>
+  <si>
+    <t>PC,ブラウザ</t>
+  </si>
+  <si>
     <t>初期表示（権限）</t>
   </si>
   <si>
@@ -69,6 +78,9 @@
   </si>
   <si>
     <t>何も選択していない状態でも、空欄が選択済になっている。</t>
+  </si>
+  <si>
+    <t>空欄の「選択してください」が選択済み。</t>
   </si>
   <si>
     <t>姓未入力</t>
@@ -165,6 +177,12 @@
     <t>「郵便番号が未入力です。」赤字表示</t>
   </si>
   <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>郵便番号未入力時に、何もエラーの表示が出ない。</t>
+  </si>
+  <si>
     <t>住所（市区町村）未入力</t>
   </si>
   <si>
@@ -191,10 +209,17 @@
     <t>「住所（番地）が未入力です。」赤字表示</t>
   </si>
   <si>
+    <t>住所（番地）未入力時に、何もエラーの表示が出ない。</t>
+  </si>
+  <si>
     <t>全項目未入力</t>
   </si>
   <si>
     <t>全項目に赤字でエラー表示</t>
+  </si>
+  <si>
+    <t>郵便番号未入力時に、何もエラーの表示が出ない。
+住所（番地）未入力時に、何もエラーの表示が出ない。</t>
   </si>
   <si>
     <t>名前（姓）形式
@@ -247,6 +272,10 @@
 ⑤名前（姓）以外の欄に値を入力する。</t>
   </si>
   <si>
+    <t>名前（名）形式
+半角英字入力時のエラー</t>
+  </si>
+  <si>
     <t>①index.htmlをエクスプローラーで表示する。
 ②アカウント登録をクリックする。
 ③regist.phpのアカウント登録の画面が表示されたことを確認する。
@@ -257,11 +286,19 @@
     <t>「名前（名）はひらがな・漢字のみ入力できます。」表示</t>
   </si>
   <si>
+    <t>名前（名）形式
+全角英字入力時のエラー</t>
+  </si>
+  <si>
     <t>①index.htmlをエクスプローラーで表示する。
 ②アカウント登録をクリックする。
 ③regist.phpのアカウント登録の画面が表示されたことを確認する。
 ④名前（姓）を入力時に全角英字入力の値を入力する。
 ⑤名前（姓）以外の欄に値を入力する。</t>
+  </si>
+  <si>
+    <t>名前（名）形式
+半角数字入力時のエラー</t>
   </si>
   <si>
     <t>①index.htmlをエクスプローラーで表示する。
@@ -698,7 +735,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -717,7 +754,9 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -730,9 +769,6 @@
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -742,11 +778,11 @@
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1024,11 +1060,19 @@
       <c r="E2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="7"/>
+      <c r="F2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I2" s="8"/>
-      <c r="J2" s="5"/>
+      <c r="J2" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9"/>
@@ -1036,19 +1080,27 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="7"/>
+      <c r="H3" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I3" s="8"/>
-      <c r="J3" s="5"/>
+      <c r="J3" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9"/>
@@ -1056,417 +1108,585 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="7">
+        <v>46090.0</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="10"/>
       <c r="B5" s="5">
         <v>4.0</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>18</v>
+      <c r="C5" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="7"/>
+        <v>23</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I5" s="8"/>
-      <c r="J5" s="5"/>
+      <c r="J5" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="11">
+      <c r="A6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="6">
         <v>5.0</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>22</v>
+      <c r="C6" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+        <v>27</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="14"/>
-      <c r="B7" s="11">
+      <c r="A7" s="13"/>
+      <c r="B7" s="6">
         <v>5.0</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>25</v>
+      <c r="C7" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="8"/>
+        <v>30</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="7">
+        <v>46090.0</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="14"/>
-      <c r="B8" s="11">
+      <c r="A8" s="13"/>
+      <c r="B8" s="6">
         <v>6.0</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>28</v>
+      <c r="C8" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="8"/>
+        <v>33</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="7">
+        <v>46090.0</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="14"/>
-      <c r="B9" s="11">
+      <c r="A9" s="13"/>
+      <c r="B9" s="6">
         <v>7.0</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>31</v>
+      <c r="C9" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="8"/>
+        <v>36</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="7">
+        <v>46090.0</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="14"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="5">
         <v>8.0</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>34</v>
+      <c r="C10" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="8"/>
+        <v>39</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="7">
+        <v>46090.0</v>
+      </c>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="14"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="5">
         <v>9.0</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>37</v>
+      <c r="C11" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="8"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="7">
+        <v>46090.0</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="14"/>
+      <c r="A12" s="13"/>
       <c r="B12" s="5">
         <v>10.0</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>40</v>
+      <c r="C12" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="11"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="8"/>
+        <v>47</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="7">
+        <v>46090.0</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="14"/>
+      <c r="A13" s="13"/>
       <c r="B13" s="5">
         <v>11.0</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>43</v>
+      <c r="C13" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="11"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="8"/>
+      <c r="G13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="7">
+        <v>46090.0</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="14"/>
+      <c r="A14" s="13"/>
       <c r="B14" s="5">
         <v>12.0</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>46</v>
+      <c r="C14" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="8"/>
+      <c r="E14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="7">
+        <v>46090.0</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="16"/>
+      <c r="A15" s="14"/>
       <c r="B15" s="5">
         <v>13.0</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="11"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="8"/>
+        <v>58</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="7">
+        <v>46090.0</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="11">
+      <c r="A16" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="6">
         <v>14.0</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8"/>
+        <v>58</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I16" s="5"/>
-      <c r="J16" s="8"/>
+      <c r="J16" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="14"/>
-      <c r="B17" s="11">
+      <c r="A17" s="13"/>
+      <c r="B17" s="6">
         <v>15.0</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8"/>
+        <v>58</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I17" s="5"/>
-      <c r="J17" s="8"/>
+      <c r="J17" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="14"/>
-      <c r="B18" s="11">
+      <c r="A18" s="13"/>
+      <c r="B18" s="6">
         <v>16.0</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="8"/>
+        <v>58</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I18" s="5"/>
-      <c r="J18" s="8"/>
+      <c r="J18" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="14"/>
-      <c r="B19" s="11">
+      <c r="A19" s="13"/>
+      <c r="B19" s="6">
         <v>17.0</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
+        <v>68</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I19" s="5"/>
-      <c r="J19" s="8"/>
+      <c r="J19" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="14"/>
-      <c r="B20" s="11">
+      <c r="A20" s="13"/>
+      <c r="B20" s="6">
         <v>18.0</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="8"/>
+        <v>68</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I20" s="5"/>
-      <c r="J20" s="8"/>
+      <c r="J20" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="14"/>
-      <c r="B21" s="11">
+      <c r="A21" s="13"/>
+      <c r="B21" s="6">
         <v>19.0</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8"/>
+        <v>68</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I21" s="5"/>
-      <c r="J21" s="8"/>
+      <c r="J21" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="14"/>
-      <c r="B22" s="11">
+      <c r="A22" s="13"/>
+      <c r="B22" s="6">
         <v>20.0</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="8"/>
+        <v>68</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I22" s="5"/>
-      <c r="J22" s="8"/>
+      <c r="J22" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="14"/>
-      <c r="B23" s="11">
+      <c r="A23" s="13"/>
+      <c r="B23" s="6">
         <v>21.0</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="8"/>
+        <v>76</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="7">
+        <v>46090.0</v>
+      </c>
       <c r="I23" s="5"/>
-      <c r="J23" s="8"/>
+      <c r="J23" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="14"/>
-      <c r="B24" s="11">
+      <c r="A24" s="13"/>
+      <c r="B24" s="6">
         <v>22.0</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="7"/>
@@ -1475,18 +1695,18 @@
       <c r="J24" s="8"/>
     </row>
     <row r="25">
-      <c r="A25" s="14"/>
-      <c r="B25" s="11">
+      <c r="A25" s="13"/>
+      <c r="B25" s="6">
         <v>23.0</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="7"/>
@@ -1495,18 +1715,18 @@
       <c r="J25" s="8"/>
     </row>
     <row r="26">
-      <c r="A26" s="14"/>
-      <c r="B26" s="11">
+      <c r="A26" s="13"/>
+      <c r="B26" s="6">
         <v>24.0</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="7"/>
@@ -1515,552 +1735,552 @@
       <c r="J26" s="8"/>
     </row>
     <row r="27">
-      <c r="A27" s="14"/>
-      <c r="B27" s="11">
+      <c r="A27" s="13"/>
+      <c r="B27" s="6">
         <v>25.0</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="11"/>
+        <v>76</v>
+      </c>
+      <c r="F27" s="6"/>
       <c r="G27" s="7"/>
       <c r="H27" s="8"/>
       <c r="I27" s="5"/>
       <c r="J27" s="8"/>
     </row>
     <row r="28">
-      <c r="A28" s="14"/>
-      <c r="B28" s="11">
+      <c r="A28" s="13"/>
+      <c r="B28" s="6">
         <v>26.0</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" s="11"/>
+        <v>76</v>
+      </c>
+      <c r="F28" s="6"/>
       <c r="G28" s="7"/>
       <c r="H28" s="8"/>
       <c r="I28" s="5"/>
       <c r="J28" s="8"/>
     </row>
     <row r="29">
-      <c r="A29" s="14"/>
-      <c r="B29" s="11">
+      <c r="A29" s="13"/>
+      <c r="B29" s="6">
         <v>27.0</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="11"/>
+        <v>86</v>
+      </c>
+      <c r="F29" s="6"/>
       <c r="G29" s="7"/>
       <c r="H29" s="8"/>
       <c r="I29" s="5"/>
       <c r="J29" s="8"/>
     </row>
     <row r="30">
-      <c r="A30" s="14"/>
-      <c r="B30" s="11">
+      <c r="A30" s="13"/>
+      <c r="B30" s="6">
         <v>28.0</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" s="11"/>
+        <v>86</v>
+      </c>
+      <c r="F30" s="6"/>
       <c r="G30" s="7"/>
       <c r="H30" s="8"/>
       <c r="I30" s="5"/>
       <c r="J30" s="8"/>
     </row>
     <row r="31">
-      <c r="A31" s="14"/>
-      <c r="B31" s="11">
+      <c r="A31" s="13"/>
+      <c r="B31" s="6">
         <v>29.0</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="11"/>
+        <v>86</v>
+      </c>
+      <c r="F31" s="6"/>
       <c r="G31" s="7"/>
       <c r="H31" s="8"/>
       <c r="I31" s="5"/>
       <c r="J31" s="8"/>
     </row>
     <row r="32">
-      <c r="A32" s="14"/>
-      <c r="B32" s="11">
+      <c r="A32" s="13"/>
+      <c r="B32" s="6">
         <v>30.0</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32" s="11"/>
+        <v>86</v>
+      </c>
+      <c r="F32" s="6"/>
       <c r="G32" s="7"/>
       <c r="H32" s="8"/>
       <c r="I32" s="5"/>
       <c r="J32" s="8"/>
     </row>
     <row r="33">
-      <c r="A33" s="14"/>
-      <c r="B33" s="11">
+      <c r="A33" s="13"/>
+      <c r="B33" s="6">
         <v>31.0</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F33" s="11"/>
+        <v>86</v>
+      </c>
+      <c r="F33" s="6"/>
       <c r="G33" s="7"/>
       <c r="H33" s="8"/>
       <c r="I33" s="5"/>
       <c r="J33" s="8"/>
     </row>
     <row r="34">
-      <c r="A34" s="14"/>
-      <c r="B34" s="11">
+      <c r="A34" s="13"/>
+      <c r="B34" s="6">
         <v>32.0</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F34" s="11"/>
+        <v>97</v>
+      </c>
+      <c r="F34" s="6"/>
       <c r="G34" s="7"/>
       <c r="H34" s="8"/>
       <c r="I34" s="5"/>
       <c r="J34" s="8"/>
     </row>
     <row r="35">
-      <c r="A35" s="14"/>
-      <c r="B35" s="11">
+      <c r="A35" s="13"/>
+      <c r="B35" s="6">
         <v>33.0</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F35" s="11"/>
+        <v>97</v>
+      </c>
+      <c r="F35" s="6"/>
       <c r="G35" s="7"/>
       <c r="H35" s="8"/>
       <c r="I35" s="5"/>
       <c r="J35" s="8"/>
     </row>
     <row r="36">
-      <c r="A36" s="14"/>
-      <c r="B36" s="11">
+      <c r="A36" s="13"/>
+      <c r="B36" s="6">
         <v>34.0</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F36" s="11"/>
+        <v>97</v>
+      </c>
+      <c r="F36" s="6"/>
       <c r="G36" s="7"/>
       <c r="H36" s="8"/>
       <c r="I36" s="5"/>
       <c r="J36" s="8"/>
     </row>
     <row r="37">
-      <c r="A37" s="14"/>
-      <c r="B37" s="11">
+      <c r="A37" s="13"/>
+      <c r="B37" s="6">
         <v>35.0</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" s="11"/>
+        <v>97</v>
+      </c>
+      <c r="F37" s="6"/>
       <c r="G37" s="7"/>
       <c r="H37" s="8"/>
       <c r="I37" s="5"/>
       <c r="J37" s="8"/>
     </row>
     <row r="38">
-      <c r="A38" s="14"/>
-      <c r="B38" s="11">
+      <c r="A38" s="13"/>
+      <c r="B38" s="6">
         <v>36.0</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F38" s="11"/>
+        <v>106</v>
+      </c>
+      <c r="F38" s="6"/>
       <c r="G38" s="7"/>
       <c r="H38" s="8"/>
       <c r="I38" s="5"/>
       <c r="J38" s="8"/>
     </row>
     <row r="39">
-      <c r="A39" s="14"/>
-      <c r="B39" s="11">
+      <c r="A39" s="13"/>
+      <c r="B39" s="6">
         <v>37.0</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F39" s="11"/>
+        <v>106</v>
+      </c>
+      <c r="F39" s="6"/>
       <c r="G39" s="7"/>
       <c r="H39" s="8"/>
       <c r="I39" s="5"/>
       <c r="J39" s="8"/>
     </row>
     <row r="40">
-      <c r="A40" s="14"/>
-      <c r="B40" s="11">
+      <c r="A40" s="13"/>
+      <c r="B40" s="6">
         <v>38.0</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="F40" s="11"/>
+        <v>106</v>
+      </c>
+      <c r="F40" s="6"/>
       <c r="G40" s="7"/>
       <c r="H40" s="8"/>
       <c r="I40" s="5"/>
       <c r="J40" s="8"/>
     </row>
     <row r="41">
-      <c r="A41" s="14"/>
-      <c r="B41" s="11">
+      <c r="A41" s="13"/>
+      <c r="B41" s="6">
         <v>39.0</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F41" s="11"/>
+        <v>113</v>
+      </c>
+      <c r="F41" s="6"/>
       <c r="G41" s="7"/>
       <c r="H41" s="8"/>
       <c r="I41" s="5"/>
       <c r="J41" s="8"/>
     </row>
     <row r="42">
-      <c r="A42" s="14"/>
-      <c r="B42" s="11">
+      <c r="A42" s="13"/>
+      <c r="B42" s="6">
         <v>40.0</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F42" s="11"/>
+        <v>113</v>
+      </c>
+      <c r="F42" s="6"/>
       <c r="G42" s="7"/>
       <c r="H42" s="8"/>
       <c r="I42" s="5"/>
       <c r="J42" s="8"/>
     </row>
     <row r="43">
-      <c r="A43" s="14"/>
-      <c r="B43" s="11">
+      <c r="A43" s="13"/>
+      <c r="B43" s="6">
         <v>41.0</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F43" s="11"/>
+        <v>113</v>
+      </c>
+      <c r="F43" s="6"/>
       <c r="G43" s="7"/>
       <c r="H43" s="8"/>
       <c r="I43" s="5"/>
       <c r="J43" s="8"/>
     </row>
     <row r="44">
-      <c r="A44" s="14"/>
-      <c r="B44" s="11">
+      <c r="A44" s="13"/>
+      <c r="B44" s="6">
         <v>42.0</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F44" s="11"/>
+        <v>120</v>
+      </c>
+      <c r="F44" s="6"/>
       <c r="G44" s="7"/>
       <c r="H44" s="8"/>
       <c r="I44" s="5"/>
       <c r="J44" s="8"/>
     </row>
     <row r="45">
-      <c r="A45" s="14"/>
-      <c r="B45" s="11">
+      <c r="A45" s="13"/>
+      <c r="B45" s="6">
         <v>43.0</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F45" s="11"/>
+        <v>120</v>
+      </c>
+      <c r="F45" s="6"/>
       <c r="G45" s="7"/>
       <c r="H45" s="8"/>
       <c r="I45" s="5"/>
       <c r="J45" s="8"/>
     </row>
     <row r="46">
-      <c r="A46" s="14"/>
-      <c r="B46" s="11">
+      <c r="A46" s="13"/>
+      <c r="B46" s="6">
         <v>44.0</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F46" s="11"/>
+        <v>120</v>
+      </c>
+      <c r="F46" s="6"/>
       <c r="G46" s="7"/>
       <c r="H46" s="8"/>
       <c r="I46" s="5"/>
       <c r="J46" s="8"/>
     </row>
     <row r="47">
-      <c r="A47" s="14"/>
-      <c r="B47" s="11">
+      <c r="A47" s="13"/>
+      <c r="B47" s="6">
         <v>45.0</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="F47" s="11"/>
+        <v>126</v>
+      </c>
+      <c r="F47" s="6"/>
       <c r="G47" s="7"/>
       <c r="H47" s="8"/>
       <c r="I47" s="5"/>
       <c r="J47" s="8"/>
     </row>
     <row r="48">
-      <c r="A48" s="14"/>
-      <c r="B48" s="11">
+      <c r="A48" s="13"/>
+      <c r="B48" s="6">
         <v>46.0</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="F48" s="11"/>
+        <v>126</v>
+      </c>
+      <c r="F48" s="6"/>
       <c r="G48" s="7"/>
       <c r="H48" s="8"/>
       <c r="I48" s="5"/>
       <c r="J48" s="8"/>
     </row>
     <row r="49">
-      <c r="A49" s="14"/>
-      <c r="B49" s="11">
+      <c r="A49" s="13"/>
+      <c r="B49" s="6">
         <v>47.0</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F49" s="11"/>
+        <v>131</v>
+      </c>
+      <c r="F49" s="6"/>
       <c r="G49" s="7"/>
       <c r="H49" s="8"/>
       <c r="I49" s="5"/>
       <c r="J49" s="8"/>
     </row>
     <row r="50">
-      <c r="A50" s="16"/>
-      <c r="B50" s="11">
+      <c r="A50" s="14"/>
+      <c r="B50" s="6">
         <v>48.0</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F50" s="11"/>
+        <v>131</v>
+      </c>
+      <c r="F50" s="6"/>
       <c r="G50" s="7"/>
       <c r="H50" s="8"/>
       <c r="I50" s="5"/>
       <c r="J50" s="8"/>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B51" s="11">
+      <c r="A51" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="6">
         <v>49.0</v>
       </c>
-      <c r="C51" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="F51" s="11"/>
+      <c r="C51" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F51" s="6"/>
       <c r="G51" s="7"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="8"/>
     </row>
     <row r="52">
-      <c r="A52" s="16"/>
-      <c r="B52" s="11">
+      <c r="A52" s="14"/>
+      <c r="B52" s="6">
         <v>50.0</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="F52" s="11"/>
+      <c r="C52" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F52" s="6"/>
       <c r="G52" s="7"/>
       <c r="H52" s="8"/>
       <c r="I52" s="5"/>
       <c r="J52" s="8"/>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="B53" s="11">
+      <c r="A53" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" s="6">
         <v>51.0</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F53" s="11"/>
+        <v>143</v>
+      </c>
+      <c r="F53" s="6"/>
       <c r="G53" s="15"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="5"/>
       <c r="J53" s="8"/>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F15 F27:F52 G53">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F23 F27:F52 G53">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/regist.php 単体テスト仕様書.xlsx
+++ b/regist.php 単体テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="145">
   <si>
     <t>テスト区分</t>
   </si>
@@ -177,12 +177,6 @@
     <t>「郵便番号が未入力です。」赤字表示</t>
   </si>
   <si>
-    <t>NG</t>
-  </si>
-  <si>
-    <t>郵便番号未入力時に、何もエラーの表示が出ない。</t>
-  </si>
-  <si>
     <t>住所（市区町村）未入力</t>
   </si>
   <si>
@@ -209,17 +203,10 @@
     <t>「住所（番地）が未入力です。」赤字表示</t>
   </si>
   <si>
-    <t>住所（番地）未入力時に、何もエラーの表示が出ない。</t>
-  </si>
-  <si>
     <t>全項目未入力</t>
   </si>
   <si>
     <t>全項目に赤字でエラー表示</t>
-  </si>
-  <si>
-    <t>郵便番号未入力時に、何もエラーの表示が出ない。
-住所（番地）未入力時に、何もエラーの表示が出ない。</t>
   </si>
   <si>
     <t>名前（姓）形式
@@ -422,7 +409,7 @@
   </si>
   <si>
     <t>パスワード形式
-全角入力のエラー</t>
+全角入力時</t>
   </si>
   <si>
     <t>①index.htmlをエクスプローラーで表示する。
@@ -432,11 +419,11 @@
 ⑤パスワード以外の欄に値を入力する。</t>
   </si>
   <si>
-    <t>「パスワードは半角英数字のみ入力できます。」表示</t>
+    <t>パスワードは半角英数字以外は入力できない</t>
   </si>
   <si>
     <t>パスワード形式
-漢字入力のエラー</t>
+漢字入力時</t>
   </si>
   <si>
     <t>①index.htmlをエクスプローラーで表示する。
@@ -447,7 +434,7 @@
   </si>
   <si>
     <t>パスワード形式
-ひらがな入力のエラー</t>
+ひらがな入力時</t>
   </si>
   <si>
     <t>①index.htmlをエクスプローラーで表示する。
@@ -458,7 +445,7 @@
   </si>
   <si>
     <t>パスワード形式
-カタカナ入力のエラー</t>
+カタカナ入力時</t>
   </si>
   <si>
     <t>①index.htmlをエクスプローラーで表示する。
@@ -479,7 +466,7 @@
 ⑤郵便番号以外の欄に値を入力する。</t>
   </si>
   <si>
-    <t>エラー表示</t>
+    <t>「郵便番号は7桁の半角数字で入力してください。」表示</t>
   </si>
   <si>
     <t>郵便番号形式
@@ -530,13 +517,13 @@
   </si>
   <si>
     <t>住所（市区町村）形式
-半角英字入力のエラー</t>
-  </si>
-  <si>
-    <t>①index.htmlをエクスプローラーで表示する。
-②アカウント登録をクリックする。
-③regist.phpのアカウント登録の画面が表示されたことを確認する。
-④住所（市区町村）を入力時に半角英字の値を入力する。
+全角数字入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④住所（市区町村）を入力時に全角数字の値を入力する。
 ⑤住所（市区町村）以外の欄に値を入力する。</t>
   </si>
   <si>
@@ -567,7 +554,14 @@
   </si>
   <si>
     <t>住所（番地）形式
-半角英字入力のエラー</t>
+全角数字入力のエラー</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④住所（番地）を入力時に全角数字の値を入力する。
+⑤住所（番地）以外の欄に値を入力する。</t>
   </si>
   <si>
     <t>姓11文字
@@ -581,7 +575,10 @@
 ⑤姓以外の欄に値を入力する。</t>
   </si>
   <si>
-    <t>入力不可 or エラー表示</t>
+    <t>入力不可</t>
+  </si>
+  <si>
+    <t>11文字以上入力しようとしても、自動的に11文字以内になる。</t>
   </si>
   <si>
     <t>名11文字
@@ -609,7 +606,16 @@
     <t>メールアドレスの形式が正しくありませんと表示</t>
   </si>
   <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>エラーの表示なし</t>
+  </si>
+  <si>
     <t>メール101文字</t>
+  </si>
+  <si>
+    <t>101字まで入力できない</t>
   </si>
   <si>
     <t>文字数チェック</t>
@@ -735,7 +741,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -780,9 +786,6 @@
     </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1317,7 +1320,7 @@
         <v>43</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>15</v>
@@ -1325,9 +1328,7 @@
       <c r="H11" s="7">
         <v>46090.0</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
         <v>16</v>
       </c>
@@ -1338,13 +1339,13 @@
         <v>10.0</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>14</v>
@@ -1366,16 +1367,16 @@
         <v>11.0</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="F13" s="6" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>15</v>
@@ -1383,9 +1384,7 @@
       <c r="H13" s="7">
         <v>46090.0</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>52</v>
-      </c>
+      <c r="I13" s="5"/>
       <c r="J13" s="5" t="s">
         <v>16</v>
       </c>
@@ -1396,16 +1395,16 @@
         <v>12.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>15</v>
@@ -1413,9 +1412,7 @@
       <c r="H14" s="7">
         <v>46090.0</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>55</v>
-      </c>
+      <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
         <v>16</v>
       </c>
@@ -1426,13 +1423,13 @@
         <v>13.0</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>14</v>
@@ -1450,19 +1447,19 @@
     </row>
     <row r="16">
       <c r="A16" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B16" s="6">
         <v>14.0</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>14</v>
@@ -1484,13 +1481,13 @@
         <v>15.0</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>14</v>
@@ -1512,13 +1509,13 @@
         <v>16.0</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>14</v>
@@ -1540,13 +1537,13 @@
         <v>17.0</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>14</v>
@@ -1568,13 +1565,13 @@
         <v>18.0</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>14</v>
@@ -1596,13 +1593,13 @@
         <v>19.0</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>14</v>
@@ -1624,13 +1621,13 @@
         <v>20.0</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>14</v>
@@ -1652,13 +1649,13 @@
         <v>21.0</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>14</v>
@@ -1680,19 +1677,27 @@
         <v>22.0</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="8"/>
+        <v>72</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I24" s="5"/>
-      <c r="J24" s="8"/>
+      <c r="J24" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13"/>
@@ -1700,19 +1705,27 @@
         <v>23.0</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="8"/>
+        <v>72</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I25" s="5"/>
-      <c r="J25" s="8"/>
+      <c r="J25" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13"/>
@@ -1720,19 +1733,27 @@
         <v>24.0</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="8"/>
+        <v>72</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I26" s="5"/>
-      <c r="J26" s="8"/>
+      <c r="J26" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13"/>
@@ -1740,19 +1761,27 @@
         <v>25.0</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8"/>
+        <v>72</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I27" s="5"/>
-      <c r="J27" s="8"/>
+      <c r="J27" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13"/>
@@ -1760,19 +1789,27 @@
         <v>26.0</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="8"/>
+        <v>72</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I28" s="5"/>
-      <c r="J28" s="8"/>
+      <c r="J28" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="13"/>
@@ -1780,19 +1817,27 @@
         <v>27.0</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="8"/>
+        <v>82</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I29" s="5"/>
-      <c r="J29" s="8"/>
+      <c r="J29" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="13"/>
@@ -1800,19 +1845,27 @@
         <v>28.0</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="8"/>
+        <v>82</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I30" s="5"/>
-      <c r="J30" s="8"/>
+      <c r="J30" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="13"/>
@@ -1820,19 +1873,27 @@
         <v>29.0</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="8"/>
+        <v>82</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I31" s="5"/>
-      <c r="J31" s="8"/>
+      <c r="J31" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13"/>
@@ -1840,19 +1901,27 @@
         <v>30.0</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="8"/>
+        <v>82</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I32" s="5"/>
-      <c r="J32" s="8"/>
+      <c r="J32" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="13"/>
@@ -1860,19 +1929,27 @@
         <v>31.0</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="8"/>
+        <v>82</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I33" s="5"/>
-      <c r="J33" s="8"/>
+      <c r="J33" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="13"/>
@@ -1880,19 +1957,27 @@
         <v>32.0</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="8"/>
+        <v>93</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I34" s="5"/>
-      <c r="J34" s="8"/>
+      <c r="J34" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="13"/>
@@ -1900,19 +1985,27 @@
         <v>33.0</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="8"/>
+        <v>93</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I35" s="5"/>
-      <c r="J35" s="8"/>
+      <c r="J35" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="13"/>
@@ -1920,19 +2013,27 @@
         <v>34.0</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="8"/>
+        <v>93</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I36" s="5"/>
-      <c r="J36" s="8"/>
+      <c r="J36" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="13"/>
@@ -1940,19 +2041,27 @@
         <v>35.0</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="8"/>
+        <v>93</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I37" s="5"/>
-      <c r="J37" s="8"/>
+      <c r="J37" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="13"/>
@@ -1960,19 +2069,27 @@
         <v>36.0</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="8"/>
+        <v>102</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I38" s="5"/>
-      <c r="J38" s="8"/>
+      <c r="J38" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="13"/>
@@ -1980,19 +2097,27 @@
         <v>37.0</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="8"/>
+        <v>102</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I39" s="5"/>
-      <c r="J39" s="8"/>
+      <c r="J39" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="13"/>
@@ -2000,19 +2125,27 @@
         <v>38.0</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F40" s="6"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="8"/>
+        <v>102</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I40" s="5"/>
-      <c r="J40" s="8"/>
+      <c r="J40" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="13"/>
@@ -2020,19 +2153,27 @@
         <v>39.0</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="8"/>
+        <v>109</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I41" s="5"/>
-      <c r="J41" s="8"/>
+      <c r="J41" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="13"/>
@@ -2040,19 +2181,27 @@
         <v>40.0</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="8"/>
+        <v>109</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I42" s="5"/>
-      <c r="J42" s="8"/>
+      <c r="J42" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="13"/>
@@ -2060,19 +2209,27 @@
         <v>41.0</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="8"/>
+        <v>109</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I43" s="5"/>
-      <c r="J43" s="8"/>
+      <c r="J43" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="13"/>
@@ -2080,19 +2237,27 @@
         <v>42.0</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F44" s="6"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="8"/>
+        <v>116</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I44" s="5"/>
-      <c r="J44" s="8"/>
+      <c r="J44" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="13"/>
@@ -2100,19 +2265,27 @@
         <v>43.0</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F45" s="6"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="8"/>
+        <v>116</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I45" s="5"/>
-      <c r="J45" s="8"/>
+      <c r="J45" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="13"/>
@@ -2120,19 +2293,27 @@
         <v>44.0</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="8"/>
+        <v>116</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I46" s="5"/>
-      <c r="J46" s="8"/>
+      <c r="J46" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="13"/>
@@ -2140,19 +2321,29 @@
         <v>45.0</v>
       </c>
       <c r="C47" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="7">
+        <v>46092.0</v>
+      </c>
+      <c r="I47" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="8"/>
+      <c r="J47" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="13"/>
@@ -2160,19 +2351,29 @@
         <v>46.0</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="8"/>
+        <v>123</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" s="7">
+        <v>46092.0</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="13"/>
@@ -2180,19 +2381,29 @@
         <v>47.0</v>
       </c>
       <c r="C49" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="F49" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="G49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="7">
+        <v>46092.0</v>
+      </c>
+      <c r="I49" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="8"/>
+      <c r="J49" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="14"/>
@@ -2203,38 +2414,56 @@
         <v>132</v>
       </c>
       <c r="D50" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F50" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F50" s="6"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="8"/>
+      <c r="G50" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="7">
+        <v>46092.0</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B51" s="6">
         <v>49.0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="F51" s="6"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="5"/>
+        <v>137</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I51" s="5"/>
-      <c r="J51" s="8"/>
+      <c r="J51" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="14"/>
@@ -2242,45 +2471,61 @@
         <v>50.0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="F52" s="6"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="8"/>
+        <v>140</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I52" s="5"/>
-      <c r="J52" s="8"/>
+      <c r="J52" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B53" s="6">
         <v>51.0</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F53" s="6"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="6"/>
+        <v>144</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="7">
+        <v>46092.0</v>
+      </c>
       <c r="I53" s="5"/>
-      <c r="J53" s="8"/>
+      <c r="J53" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F23 F27:F52 G53">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F53">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/regist.php 単体テスト仕様書.xlsx
+++ b/regist.php 単体テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="143">
   <si>
     <t>テスト区分</t>
   </si>
@@ -606,16 +606,14 @@
     <t>メールアドレスの形式が正しくありませんと表示</t>
   </si>
   <si>
-    <t>NG</t>
-  </si>
-  <si>
-    <t>エラーの表示なし</t>
-  </si>
-  <si>
     <t>メール101文字</t>
   </si>
   <si>
-    <t>101字まで入力できない</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④メールアドレスを入力時に101文字以上の値を入力する。
+⑤メールアドレス以外の欄に値を入力する。</t>
   </si>
   <si>
     <t>文字数チェック</t>
@@ -1070,7 +1068,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="5" t="s">
@@ -1098,7 +1096,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="5" t="s">
@@ -1126,7 +1124,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>21</v>
@@ -1156,7 +1154,7 @@
         <v>15</v>
       </c>
       <c r="H5" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="5" t="s">
@@ -1186,7 +1184,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="5" t="s">
@@ -1214,7 +1212,7 @@
         <v>15</v>
       </c>
       <c r="H7" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
@@ -1242,7 +1240,7 @@
         <v>15</v>
       </c>
       <c r="H8" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
@@ -1270,7 +1268,7 @@
         <v>15</v>
       </c>
       <c r="H9" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
@@ -1298,7 +1296,7 @@
         <v>15</v>
       </c>
       <c r="H10" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
@@ -1326,7 +1324,7 @@
         <v>15</v>
       </c>
       <c r="H11" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
@@ -1354,7 +1352,7 @@
         <v>15</v>
       </c>
       <c r="H12" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
@@ -1382,7 +1380,7 @@
         <v>15</v>
       </c>
       <c r="H13" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5" t="s">
@@ -1410,7 +1408,7 @@
         <v>15</v>
       </c>
       <c r="H14" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
@@ -1438,7 +1436,7 @@
         <v>15</v>
       </c>
       <c r="H15" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
@@ -1468,7 +1466,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="s">
@@ -1496,7 +1494,7 @@
         <v>15</v>
       </c>
       <c r="H17" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
@@ -1524,7 +1522,7 @@
         <v>15</v>
       </c>
       <c r="H18" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5" t="s">
@@ -1552,7 +1550,7 @@
         <v>15</v>
       </c>
       <c r="H19" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
@@ -1580,7 +1578,7 @@
         <v>15</v>
       </c>
       <c r="H20" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I20" s="5"/>
       <c r="J20" s="5" t="s">
@@ -1608,7 +1606,7 @@
         <v>15</v>
       </c>
       <c r="H21" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
@@ -1636,7 +1634,7 @@
         <v>15</v>
       </c>
       <c r="H22" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
@@ -1664,7 +1662,7 @@
         <v>15</v>
       </c>
       <c r="H23" s="7">
-        <v>46090.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
@@ -1692,7 +1690,7 @@
         <v>15</v>
       </c>
       <c r="H24" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
@@ -1720,7 +1718,7 @@
         <v>15</v>
       </c>
       <c r="H25" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
@@ -1748,7 +1746,7 @@
         <v>15</v>
       </c>
       <c r="H26" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
@@ -1776,7 +1774,7 @@
         <v>15</v>
       </c>
       <c r="H27" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I27" s="5"/>
       <c r="J27" s="5" t="s">
@@ -1804,7 +1802,7 @@
         <v>15</v>
       </c>
       <c r="H28" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I28" s="5"/>
       <c r="J28" s="5" t="s">
@@ -1832,7 +1830,7 @@
         <v>15</v>
       </c>
       <c r="H29" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5" t="s">
@@ -1860,7 +1858,7 @@
         <v>15</v>
       </c>
       <c r="H30" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
@@ -1888,7 +1886,7 @@
         <v>15</v>
       </c>
       <c r="H31" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5" t="s">
@@ -1916,7 +1914,7 @@
         <v>15</v>
       </c>
       <c r="H32" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5" t="s">
@@ -1944,7 +1942,7 @@
         <v>15</v>
       </c>
       <c r="H33" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5" t="s">
@@ -1972,7 +1970,7 @@
         <v>15</v>
       </c>
       <c r="H34" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="5" t="s">
@@ -2000,7 +1998,7 @@
         <v>15</v>
       </c>
       <c r="H35" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5" t="s">
@@ -2028,7 +2026,7 @@
         <v>15</v>
       </c>
       <c r="H36" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5" t="s">
@@ -2056,7 +2054,7 @@
         <v>15</v>
       </c>
       <c r="H37" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5" t="s">
@@ -2084,7 +2082,7 @@
         <v>15</v>
       </c>
       <c r="H38" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
@@ -2112,7 +2110,7 @@
         <v>15</v>
       </c>
       <c r="H39" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="5" t="s">
@@ -2140,7 +2138,7 @@
         <v>15</v>
       </c>
       <c r="H40" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I40" s="5"/>
       <c r="J40" s="5" t="s">
@@ -2168,7 +2166,7 @@
         <v>15</v>
       </c>
       <c r="H41" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5" t="s">
@@ -2196,7 +2194,7 @@
         <v>15</v>
       </c>
       <c r="H42" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5" t="s">
@@ -2224,7 +2222,7 @@
         <v>15</v>
       </c>
       <c r="H43" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5" t="s">
@@ -2252,7 +2250,7 @@
         <v>15</v>
       </c>
       <c r="H44" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I44" s="5"/>
       <c r="J44" s="5" t="s">
@@ -2280,7 +2278,7 @@
         <v>15</v>
       </c>
       <c r="H45" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5" t="s">
@@ -2308,7 +2306,7 @@
         <v>15</v>
       </c>
       <c r="H46" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5" t="s">
@@ -2336,7 +2334,7 @@
         <v>15</v>
       </c>
       <c r="H47" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>124</v>
@@ -2366,7 +2364,7 @@
         <v>15</v>
       </c>
       <c r="H48" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I48" s="5" t="s">
         <v>124</v>
@@ -2390,17 +2388,15 @@
         <v>129</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H49" s="7">
-        <v>46092.0</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>131</v>
-      </c>
+        <v>46111.0</v>
+      </c>
+      <c r="I49" s="5"/>
       <c r="J49" s="5" t="s">
         <v>16</v>
       </c>
@@ -2411,46 +2407,44 @@
         <v>48.0</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>129</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>15</v>
       </c>
       <c r="H50" s="7">
-        <v>46092.0</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>133</v>
-      </c>
+        <v>46111.0</v>
+      </c>
+      <c r="I50" s="5"/>
       <c r="J50" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B51" s="6">
         <v>49.0</v>
       </c>
       <c r="C51" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>137</v>
-      </c>
       <c r="F51" s="6" t="s">
         <v>14</v>
       </c>
@@ -2458,7 +2452,7 @@
         <v>15</v>
       </c>
       <c r="H51" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I51" s="5"/>
       <c r="J51" s="5" t="s">
@@ -2471,14 +2465,14 @@
         <v>50.0</v>
       </c>
       <c r="C52" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="F52" s="6" t="s">
         <v>14</v>
       </c>
@@ -2486,7 +2480,7 @@
         <v>15</v>
       </c>
       <c r="H52" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I52" s="5"/>
       <c r="J52" s="5" t="s">
@@ -2495,20 +2489,20 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B53" s="6">
         <v>51.0</v>
       </c>
       <c r="C53" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>144</v>
-      </c>
       <c r="F53" s="6" t="s">
         <v>14</v>
       </c>
@@ -2516,7 +2510,7 @@
         <v>15</v>
       </c>
       <c r="H53" s="7">
-        <v>46092.0</v>
+        <v>46111.0</v>
       </c>
       <c r="I53" s="5"/>
       <c r="J53" s="5" t="s">
